--- a/爬虫数据来源.xlsx
+++ b/爬虫数据来源.xlsx
@@ -1,295 +1,185 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12060"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12060" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
-  <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>新闻</t>
-  </si>
-  <si>
-    <t>栏目</t>
-  </si>
-  <si>
-    <t>来源</t>
-  </si>
-  <si>
-    <t>格式</t>
-  </si>
-  <si>
-    <t>领导活动</t>
-  </si>
-  <si>
-    <t>东城要闻</t>
-  </si>
-  <si>
-    <t>https://www.bjdch.gov.cn/ywdt/dcyw/</t>
-  </si>
-  <si>
-    <t>1.格式问题：标题格式加粗（标题文字宋体 五号 段落格式：居中对齐 行距：单倍行距 1倍）；
-2.正文首行空两格（字体为宋体 五号  段落格式：左对齐 行距：单倍行距 1倍）；
-3.单位动态的作者为：各单位   其他有作者就为原作者  没作者就无
-4.图片格式：png/jpg，图片位置于原文位置保持一致，需单独保存于原路径下。</t>
-  </si>
-  <si>
-    <t>单位动态</t>
-  </si>
-  <si>
-    <t>部门动态</t>
-  </si>
-  <si>
-    <t>https://www.bjdch.gov.cn/ywdt/bmdt/</t>
-  </si>
-  <si>
-    <t>时政新闻</t>
-  </si>
-  <si>
-    <t>高层动态</t>
-  </si>
-  <si>
-    <t>http://cpc.people.com.cn/GB/64093/64094/index.html</t>
-  </si>
-  <si>
-    <t>重要新闻</t>
-  </si>
-  <si>
-    <t>https://www.xuexi.cn/98d5ae483720f701144e4dabf99a4a34/5957f69bffab66811b99940516ec8784.html</t>
-  </si>
-  <si>
-    <t>党建要闻</t>
-  </si>
-  <si>
-    <t>http://www.dangjian.cn/djyw/list_50750_1.html</t>
-  </si>
-  <si>
-    <t>哲学社会科学</t>
-  </si>
-  <si>
-    <t>https://www.xuexi.cn/xxqg.html?id=20e4b1053c154447ad9485d9cdc0e47e</t>
-  </si>
-  <si>
-    <t>中共党史</t>
-  </si>
-  <si>
-    <t>学史明理</t>
-  </si>
-  <si>
-    <t>http://www.dangjian.cn/xsml/list_50765_1.html</t>
-  </si>
-  <si>
-    <t>党史故事</t>
-  </si>
-  <si>
-    <t>https://www.xuexi.cn/a626e7afac9036a3c48a3db17cdf0d6b/5957f69bffab66811b99940516ec8784.html</t>
-  </si>
-  <si>
-    <t>党史研究</t>
-  </si>
-  <si>
-    <t>https://www.xuexi.cn/e85d4f098b1153e29d96cec73c8d97c9/5957f69bffab66811b99940516ec8784.html</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="14"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -487,7 +377,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -654,208 +544,220 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="11" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="6" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="6" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -909,11 +811,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1165,213 +1130,358 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="15.625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="122.375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="58.25" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col width="15.625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="16.5" customWidth="1" style="2" min="2" max="2"/>
+    <col width="18.25" customWidth="1" style="2" min="3" max="3"/>
+    <col width="122.375" customWidth="1" style="2" min="4" max="4"/>
+    <col width="58.25" customWidth="1" style="2" min="5" max="5"/>
+    <col width="9" customWidth="1" style="2" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20" customHeight="1" spans="1:5">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" ht="20" customFormat="1" customHeight="1" s="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>新闻</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>栏目</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>格式</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>列表区域XPath</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>分页URL模板</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>渲染模式</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" s="17">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>领导活动</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>东城要闻</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>https://www.bjdch.gov.cn/ywdt/dcyw/</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>1.格式问题：标题格式加粗（标题文字宋体 五号 段落格式：居中对齐 行距：单倍行距 1倍）；
+2.正文首行空两格（字体为宋体 五号  段落格式：左对齐 行距：单倍行距 1倍）；
+3.单位动态的作者为：各单位   其他有作者就为原作者  没作者就无
+4.图片格式：png/jpg，图片位置于原文位置保持一致，需单独保存于原路径下。</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>/html/body/div[1]</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>index_{page}.html</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="17">
+      <c r="A3" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>单位动态</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>部门动态</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>https://www.bjdch.gov.cn/ywdt/bmdt/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>/html/body/div[1]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>index_{page}.html</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="17">
+      <c r="A4" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>时政新闻</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>高层动态</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64093/64094/index.html</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>/html/body/div[6]/div[1]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>index{page}.html</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="17">
+      <c r="A5" s="16" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>重要新闻</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>https://www.xuexi.cn/98d5ae483720f701144e4dabf99a4a34/5957f69bffab66811b99940516ec8784.html</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:5">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
+    <row r="6" ht="20" customHeight="1" s="17">
+      <c r="A6" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>党建要闻</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>党建要闻</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>http://www.dangjian.cn/djyw/list_50750_1.html</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" s="17">
+      <c r="A7" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>哲学社会科学</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>https://www.xuexi.cn/xxqg.html?id=20e4b1053c154447ad9485d9cdc0e47e</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" s="17">
+      <c r="A8" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>中共党史</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>学史明理</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>http://www.dangjian.cn/xsml/list_50765_1.html</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="17">
+      <c r="A9" s="16" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="19" t="n"/>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>党史故事</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>https://www.xuexi.cn/a626e7afac9036a3c48a3db17cdf0d6b/5957f69bffab66811b99940516ec8784.html</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
     </row>
-    <row r="3" ht="20" customHeight="1" spans="1:5">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
+    <row r="10" ht="20" customHeight="1" s="17">
+      <c r="A10" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="8"/>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>党史研究</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>https://www.xuexi.cn/e85d4f098b1153e29d96cec73c8d97c9/5957f69bffab66811b99940516ec8784.html</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:5">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="8"/>
-    </row>
-    <row r="5" ht="20" customHeight="1" spans="1:5">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:5">
-      <c r="A6" s="5">
-        <v>5</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="8"/>
-    </row>
-    <row r="7" ht="20" customHeight="1" spans="1:5">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="8"/>
-    </row>
-    <row r="8" ht="20" customHeight="1" spans="1:5">
-      <c r="A8" s="5">
-        <v>7</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="8"/>
-    </row>
-    <row r="9" ht="20" customHeight="1" spans="1:5">
-      <c r="A9" s="5">
-        <v>8</v>
-      </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="8"/>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="1:5">
-      <c r="A10" s="5">
-        <v>9</v>
-      </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="8"/>
-    </row>
-    <row r="11" ht="20" customHeight="1"/>
-    <row r="12" ht="20" customHeight="1"/>
-    <row r="13" ht="20" customHeight="1"/>
-    <row r="14" ht="20" customHeight="1"/>
-    <row r="15" ht="20" customHeight="1"/>
-    <row r="16" ht="20" customHeight="1"/>
-    <row r="17" ht="20" customHeight="1"/>
-    <row r="18" ht="20" customHeight="1"/>
-    <row r="19" ht="20" customHeight="1"/>
-    <row r="20" ht="20" customHeight="1"/>
-    <row r="21" ht="20" customHeight="1"/>
-    <row r="22" ht="20" customHeight="1"/>
-    <row r="23" ht="20" customHeight="1"/>
-    <row r="24" ht="20" customHeight="1"/>
-    <row r="25" ht="20" customHeight="1"/>
-    <row r="26" ht="20" customHeight="1"/>
-    <row r="27" ht="20" customHeight="1"/>
-    <row r="28" ht="20" customHeight="1"/>
-    <row r="29" ht="20" customHeight="1"/>
-    <row r="30" ht="20" customHeight="1"/>
-    <row r="31" ht="20" customHeight="1"/>
-    <row r="32" ht="20" customHeight="1"/>
-    <row r="33" ht="20" customHeight="1"/>
-    <row r="34" ht="20" customHeight="1"/>
-    <row r="35" ht="20" customHeight="1"/>
-    <row r="36" ht="20" customHeight="1"/>
-    <row r="37" ht="20" customHeight="1"/>
-    <row r="38" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1" s="17"/>
+    <row r="12" ht="20" customHeight="1" s="17"/>
+    <row r="13" ht="20" customHeight="1" s="17"/>
+    <row r="14" ht="20" customHeight="1" s="17"/>
+    <row r="15" ht="20" customHeight="1" s="17"/>
+    <row r="16" ht="20" customHeight="1" s="17"/>
+    <row r="17" ht="20" customHeight="1" s="17"/>
+    <row r="18" ht="20" customHeight="1" s="17"/>
+    <row r="19" ht="20" customHeight="1" s="17"/>
+    <row r="20" ht="20" customHeight="1" s="17"/>
+    <row r="21" ht="20" customHeight="1" s="17"/>
+    <row r="22" ht="20" customHeight="1" s="17"/>
+    <row r="23" ht="20" customHeight="1" s="17"/>
+    <row r="24" ht="20" customHeight="1" s="17"/>
+    <row r="25" ht="20" customHeight="1" s="17"/>
+    <row r="26" ht="20" customHeight="1" s="17"/>
+    <row r="27" ht="20" customHeight="1" s="17"/>
+    <row r="28" ht="20" customHeight="1" s="17"/>
+    <row r="29" ht="20" customHeight="1" s="17"/>
+    <row r="30" ht="20" customHeight="1" s="17"/>
+    <row r="31" ht="20" customHeight="1" s="17"/>
+    <row r="32" ht="20" customHeight="1" s="17"/>
+    <row r="33" ht="20" customHeight="1" s="17"/>
+    <row r="34" ht="20" customHeight="1" s="17"/>
+    <row r="35" ht="20" customHeight="1" s="17"/>
+    <row r="36" ht="20" customHeight="1" s="17"/>
+    <row r="37" ht="20" customHeight="1" s="17"/>
+    <row r="38" ht="20" customHeight="1" s="17"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B4:B5"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B4:B5"/>
     <mergeCell ref="E2:E10"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" display="http://cpc.people.com.cn/GB/64093/64094/index.html" tooltip="http://cpc.people.com.cn/GB/64093/64094/index.html"/>
-    <hyperlink ref="D2" r:id="rId2" display="https://www.bjdch.gov.cn/ywdt/dcyw/" tooltip="https://www.bjdch.gov.cn/ywdt/dcyw/"/>
-    <hyperlink ref="D3" r:id="rId3" display="https://www.bjdch.gov.cn/ywdt/bmdt/" tooltip="https://www.bjdch.gov.cn/ywdt/bmdt/"/>
-    <hyperlink ref="D5" r:id="rId4" display="https://www.xuexi.cn/98d5ae483720f701144e4dabf99a4a34/5957f69bffab66811b99940516ec8784.html"/>
-    <hyperlink ref="D6" r:id="rId5" display="http://www.dangjian.cn/djyw/list_50750_1.html"/>
-    <hyperlink ref="D8" r:id="rId6" display="http://www.dangjian.cn/xsml/list_50765_1.html"/>
-    <hyperlink ref="D7" r:id="rId7" display="https://www.xuexi.cn/xxqg.html?id=20e4b1053c154447ad9485d9cdc0e47e"/>
-    <hyperlink ref="D9" r:id="rId8" display="https://www.xuexi.cn/a626e7afac9036a3c48a3db17cdf0d6b/5957f69bffab66811b99940516ec8784.html" tooltip="https://www.xuexi.cn/a626e7afac9036a3c48a3db17cdf0d6b/5957f69bffab66811b99940516ec8784.html"/>
-    <hyperlink ref="D10" r:id="rId9" display="https://www.xuexi.cn/e85d4f098b1153e29d96cec73c8d97c9/5957f69bffab66811b99940516ec8784.html" tooltip="https://www.xuexi.cn/e85d4f098b1153e29d96cec73c8d97c9/5957f69bffab66811b99940516ec8784.html"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" tooltip="https://www.bjdch.gov.cn/ywdt/dcyw/" display="https://www.bjdch.gov.cn/ywdt/dcyw/" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" tooltip="https://www.bjdch.gov.cn/ywdt/bmdt/" display="https://www.bjdch.gov.cn/ywdt/bmdt/" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" tooltip="http://cpc.people.com.cn/GB/64093/64094/index.html" display="http://cpc.people.com.cn/GB/64093/64094/index.html" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" display="https://www.xuexi.cn/98d5ae483720f701144e4dabf99a4a34/5957f69bffab66811b99940516ec8784.html" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" display="http://www.dangjian.cn/djyw/list_50750_1.html" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" display="https://www.xuexi.cn/xxqg.html?id=20e4b1053c154447ad9485d9cdc0e47e" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" display="http://www.dangjian.cn/xsml/list_50765_1.html" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" tooltip="https://www.xuexi.cn/a626e7afac9036a3c48a3db17cdf0d6b/5957f69bffab66811b99940516ec8784.html" display="https://www.xuexi.cn/a626e7afac9036a3c48a3db17cdf0d6b/5957f69bffab66811b99940516ec8784.html" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" tooltip="https://www.xuexi.cn/e85d4f098b1153e29d96cec73c8d97c9/5957f69bffab66811b99940516ec8784.html" display="https://www.xuexi.cn/e85d4f098b1153e29d96cec73c8d97c9/5957f69bffab66811b99940516ec8784.html" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>